--- a/Data/EXCEL/Transfer/salemon/20240711/6693-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6693-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3581A0C-D32F-4CF8-B70D-C3E9A8A0D765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BD04DD1-E3B9-43D1-A058-A27705A8A51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{CFDFA2FD-1413-4D9B-9FBA-DA3CF4A4B4A0}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{5449897A-00A8-4540-A1FB-CC3151685D34}"/>
   </bookViews>
   <sheets>
     <sheet name="6693-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,27 +1261,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B9D9A6-616C-4A41-86EC-11990F8771A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC5DA68-CD6E-4744-8677-C920C8CC4126}">
   <dimension ref="A1:Q155"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1308,7 +1308,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1390,7 +1390,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1429,7 +1429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>-0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>-29.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>-30.4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>-31.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>-33.9</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>-34.299999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>-33.9</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>-33.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>-33.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>-33.700000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>-40.9</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>-2.02</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>-6.59</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5298,392 +5298,392 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>43252</v>
       </c>
